--- a/data/1.abstracting/26_07_deduplicated_processed.xlsx
+++ b/data/1.abstracting/26_07_deduplicated_processed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/BESSI/living_SEB_review/data/1.abstracting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="8_{B93B15B9-AA6B-45F7-B153-B251339DF6C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F2EF24E-CF0D-4F81-ADCE-7100F3AE1E06}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="8_{B93B15B9-AA6B-45F7-B153-B251339DF6C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89B6915E-FAB9-460D-9E6A-CBF27BDC6991}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E60670E3-24D4-4F68-BFAE-D1A286DBBF0B}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{E60670E3-24D4-4F68-BFAE-D1A286DBBF0B}"/>
   </bookViews>
   <sheets>
     <sheet name="articles" sheetId="1" r:id="rId1"/>
